--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3335.19</v>
+        <v>3482.48</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11078.22</v>
+        <v>11567.46</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1491.92</v>
+        <v>1557.8</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2517.6</v>
+        <v>2628.79</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1010.96</v>
+        <v>1055.61</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>41420.78</v>
+        <v>43250.01</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4427.06</v>
+        <v>4622.57</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>901.21</v>
+        <v>941.01</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1102.45</v>
+        <v>1151.13</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2610.72</v>
+        <v>2726.02</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2449.31</v>
+        <v>2520.45</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1396.65</v>
+        <v>1437.22</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8156.95</v>
+        <v>8393.889999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>47577.16</v>
+        <v>48959.11</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8174.8</v>
+        <v>8412.25</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7067.4</v>
+        <v>7272.69</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3376.28</v>
+        <v>3474.35</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8399.110000000001</v>
+        <v>8643.07</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1377.19</v>
+        <v>1417.19</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2313.26</v>
+        <v>2380.45</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>772.49</v>
+        <v>794.9299999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5291.67</v>
+        <v>5312.53</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10991.77</v>
+        <v>11035.11</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>9694.540000000001</v>
+        <v>9732.76</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5838.29</v>
+        <v>5861.31</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>15118.27</v>
+        <v>15177.88</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4793.77</v>
+        <v>4812.67</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4200.75</v>
+        <v>4217.31</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6812.35</v>
+        <v>6839.2</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3780.47</v>
+        <v>3795.38</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>10923.2</v>
+        <v>10966.27</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6396.69</v>
+        <v>6421.91</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5428.21</v>
+        <v>5449.61</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1846.94</v>
+        <v>1854.22</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3256.58</v>
+        <v>3310.25</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2089.32</v>
+        <v>2123.75</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5785.99</v>
+        <v>5881.35</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4853.39</v>
+        <v>4933.38</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>13162.16</v>
+        <v>13379.09</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4641.23</v>
+        <v>4717.73</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5493.4</v>
+        <v>5583.94</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>9890.950000000001</v>
+        <v>10053.97</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>765.72</v>
+        <v>778.34</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4899.19</v>
+        <v>4979.94</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4867.8</v>
+        <v>4948.03</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>10237.82</v>
+        <v>10406.55</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1137.69</v>
+        <v>1140.49</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3129.27</v>
+        <v>3136.96</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>38773.65</v>
+        <v>38869.05</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9029.33</v>
+        <v>9051.549999999999</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3164.99</v>
+        <v>3172.77</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1332.93</v>
+        <v>1336.21</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2118.24</v>
+        <v>2123.45</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2063.78</v>
+        <v>2068.86</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4497.68</v>
+        <v>4508.75</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3246.71</v>
+        <v>3254.7</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6145.14</v>
+        <v>6066.03</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3135.69</v>
+        <v>3095.32</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>881.8</v>
+        <v>870.45</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>9015.389999999999</v>
+        <v>8899.32</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2811.07</v>
+        <v>2774.88</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4736.29</v>
+        <v>4675.31</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>948.71</v>
+        <v>936.5</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>22809.22</v>
+        <v>22515.58</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2982.93</v>
+        <v>2944.53</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2044.84</v>
+        <v>2018.51</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>7621.09</v>
+        <v>7522.97</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3255.7</v>
+        <v>3213.78</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>9465.01</v>
+        <v>9343.16</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>6546.89</v>
+        <v>6462.6</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>5693.05</v>
+        <v>5619.76</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1566.18</v>
+        <v>1555.12</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>21968.76</v>
+        <v>21813.73</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>16400.39</v>
+        <v>16284.65</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>6305.68</v>
+        <v>6261.18</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3262.2</v>
+        <v>3239.17</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>4280.06</v>
+        <v>4249.86</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4283.1</v>
+        <v>4252.87</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1110.59</v>
+        <v>1102.76</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>18324.14</v>
+        <v>18194.83</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>20589.65</v>
+        <v>20444.34</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>6960.09</v>
+        <v>6910.97</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1726.36</v>
+        <v>1714.17</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2463</v>
+        <v>2445.62</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5754.52</v>
+        <v>5713.91</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>878.22</v>
+        <v>894.14</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8611.290000000001</v>
+        <v>8767.42</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>816.51</v>
+        <v>831.3099999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>995.96</v>
+        <v>1014.01</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1175.75</v>
+        <v>1197.07</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>795.9299999999999</v>
+        <v>810.36</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1909.91</v>
+        <v>1944.54</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1625.46</v>
+        <v>1654.93</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1016.28</v>
+        <v>1034.7</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1403.81</v>
+        <v>1429.26</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1017.5</v>
+        <v>1035.95</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>6280.05</v>
+        <v>6393.91</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>848.4400000000001</v>
+        <v>863.8200000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>974.7</v>
+        <v>992.37</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4158.22</v>
+        <v>4233.62</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>12402.21</v>
+        <v>12627.07</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4405.74</v>
+        <v>4485.62</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>777.95</v>
+        <v>792.05</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>19798.82</v>
+        <v>20157.79</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>40158.19</v>
+        <v>40787.25</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2961.49</v>
+        <v>3007.88</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1645.52</v>
+        <v>1671.3</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>28274.79</v>
+        <v>28717.7</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3076.05</v>
+        <v>3124.24</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>7621.09</v>
+        <v>7740.47</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3004.64</v>
+        <v>3051.71</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6288.12</v>
+        <v>6386.62</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1250.59</v>
+        <v>1270.18</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>10275.93</v>
+        <v>10436.9</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>7940.49</v>
+        <v>8064.88</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2509.89</v>
+        <v>2549.2</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1003.95</v>
+        <v>1019.68</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>7409.38</v>
+        <v>7525.45</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5542.57</v>
+        <v>5629.39</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1219.72</v>
+        <v>1238.83</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>24678.79</v>
+        <v>24677.52</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2952.63</v>
+        <v>2952.48</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>4060.76</v>
+        <v>4060.55</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2960.18</v>
+        <v>2960.03</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2447.31</v>
+        <v>2447.19</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>961.55</v>
+        <v>961.5</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>13031.72</v>
+        <v>13031.05</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3806.25</v>
+        <v>3806.05</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>891.63</v>
+        <v>891.58</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>14242.44</v>
+        <v>14241.71</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2999.94</v>
+        <v>2999.79</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2023.53</v>
+        <v>2023.42</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1348.31</v>
+        <v>1348.24</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1472.72</v>
+        <v>1472.64</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2196.01</v>
+        <v>2195.9</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1549.8</v>
+        <v>1549.72</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1095.62</v>
+        <v>1095.56</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>4552.15</v>
+        <v>4551.91</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1772.99</v>
+        <v>1772.89</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1695.75</v>
+        <v>1695.66</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>9475.33</v>
+        <v>9474.84</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>8616.43</v>
+        <v>8577.91</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2828.19</v>
+        <v>2815.54</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>775.4400000000001</v>
+        <v>771.97</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>4660.84</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>7100.63</v>
+        <v>7068.88</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>10359.5</v>
+        <v>10313.18</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>7027.68</v>
+        <v>6996.26</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>24740.27</v>
+        <v>24629.64</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>11247.21</v>
+        <v>11196.92</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>14836.9</v>
+        <v>14849.69</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>3221.61</v>
+        <v>3224.39</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>861.8200000000001</v>
+        <v>862.5700000000001</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3610.75</v>
+        <v>3613.86</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>4923.31</v>
+        <v>4927.55</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2342.93</v>
+        <v>2344.95</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>8078.32</v>
+        <v>8085.28</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>783.92</v>
+        <v>784.6</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1369.84</v>
+        <v>1371.02</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>7223.85</v>
+        <v>7230.07</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>9042.549999999999</v>
+        <v>9050.34</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>6814.92</v>
+        <v>6820.79</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1881.66</v>
+        <v>1883.28</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>898.62</v>
+        <v>899.39</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1254.23</v>
+        <v>1255.31</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>6887.51</v>
+        <v>6893.44</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3209.09</v>
+        <v>3211.85</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>34612.14</v>
+        <v>34641.96</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6024.06</v>
+        <v>6029.25</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1591.56</v>
+        <v>1592.93</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>26829.89</v>
+        <v>26853</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>913.75</v>
+        <v>914.54</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>856.9</v>
+        <v>857.64</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1377.06</v>
+        <v>1378.24</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>37946.96</v>
+        <v>38103.72</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3929.27</v>
+        <v>3945.5</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1849.05</v>
+        <v>1856.68</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5651.72</v>
+        <v>5675.07</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>810.6</v>
+        <v>813.95</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>783.92</v>
+        <v>787.16</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2454.56</v>
+        <v>2464.7</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>34613.8</v>
+        <v>34756.79</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>873.64</v>
+        <v>877.25</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>17912.26</v>
+        <v>17986.25</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1107.17</v>
+        <v>1111.74</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>4662.87</v>
+        <v>4682.13</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1254.28</v>
+        <v>1259.46</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2104.64</v>
+        <v>2113.34</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>19906.29</v>
+        <v>19988.52</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>11864.9</v>
+        <v>11913.91</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2007.91</v>
+        <v>2016.2</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1947.05</v>
+        <v>1955.09</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>4111.87</v>
+        <v>4100.52</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>788.77</v>
+        <v>786.59</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3060.7</v>
+        <v>3052.26</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2415.48</v>
+        <v>2408.82</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2626.18</v>
+        <v>2618.94</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>4806.6</v>
+        <v>4793.34</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>12136.81</v>
+        <v>12103.33</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3720.56</v>
+        <v>3710.3</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1453.55</v>
+        <v>1449.54</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>23653.57</v>
+        <v>23588.32</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>7037.26</v>
+        <v>7017.85</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>20559.34</v>
+        <v>20502.62</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>820.8</v>
+        <v>818.54</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2637.72</v>
+        <v>2630.45</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>8004.8</v>
+        <v>7982.72</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>26873.35</v>
+        <v>26799.23</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1770.77</v>
+        <v>1765.89</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1665.22</v>
+        <v>1660.63</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2205.96</v>
+        <v>2199.88</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2072.36</v>
+        <v>2066.65</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>72731.92</v>
+        <v>72531.3</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>3066.48</v>
+        <v>3058.02</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1628.77</v>
+        <v>1624.27</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>10717.19</v>
+        <v>10593.47</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2239.63</v>
+        <v>2213.78</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2227.37</v>
+        <v>2201.65</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2424.07</v>
+        <v>2396.08</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1671.6</v>
+        <v>1652.31</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2353.34</v>
+        <v>2326.17</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>6628.19</v>
+        <v>6551.67</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3792.8</v>
+        <v>3749.01</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2301.76</v>
+        <v>2275.18</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>7913.16</v>
+        <v>7821.81</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>5227.17</v>
+        <v>5166.83</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2191.91</v>
+        <v>2166.61</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2116</v>
+        <v>2091.57</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>59421.97</v>
+        <v>58735.99</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>7822.38</v>
+        <v>7732.07</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>5415.65</v>
+        <v>5353.13</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>36868.09</v>
+        <v>36442.47</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>48007.49</v>
+        <v>47453.27</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>3267.02</v>
+        <v>3229.31</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3261.88</v>
+        <v>3224.23</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2341.73</v>
+        <v>2314.69</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>5885.19</v>
+        <v>5817.25</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5476.28</v>
+        <v>5413.06</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>934.45</v>
+        <v>923.67</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>7487.26</v>
+        <v>7400.82</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>972.05</v>
+        <v>960.83</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>36839.35</v>
+        <v>36289.88</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>6636.59</v>
+        <v>6537.6</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>5752.43</v>
+        <v>5666.63</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2865.81</v>
+        <v>2823.06</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>11905.95</v>
+        <v>11728.37</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>19596.55</v>
+        <v>19304.26</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1334</v>
+        <v>1314.11</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1558.81</v>
+        <v>1535.56</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2309.1</v>
+        <v>2274.66</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>6271.38</v>
+        <v>6177.84</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>893.39</v>
+        <v>880.0599999999999</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>10978.83</v>
+        <v>10815.07</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2833.05</v>
+        <v>2790.8</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>888.25</v>
+        <v>883.15</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2629.21</v>
+        <v>2614.11</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1821.54</v>
+        <v>1811.08</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>7746.6</v>
+        <v>7702.1</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>15936.93</v>
+        <v>15845.38</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2122.45</v>
+        <v>2110.26</v>
       </c>
     </row>
     <row r="262">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1822.99</v>
+        <v>1812.52</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1647.89</v>
+        <v>1638.42</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3365.27</v>
+        <v>3345.94</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>4935.94</v>
+        <v>4907.59</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>25678.57</v>
+        <v>25531.07</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>9362.620000000001</v>
+        <v>9308.84</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>4298.02</v>
+        <v>4273.33</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1344.24</v>
+        <v>1336.52</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1467.61</v>
+        <v>1459.18</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>8067.38</v>
+        <v>8021.04</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>979.59</v>
+        <v>973.97</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>3056.63</v>
+        <v>3039.07</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1102.44</v>
+        <v>1096.1</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1259.79</v>
+        <v>1251.72</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>37349.3</v>
+        <v>37110.02</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2703.79</v>
+        <v>2686.47</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>4492.47</v>
+        <v>4463.69</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2745.61</v>
+        <v>2728.02</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>3390.79</v>
+        <v>3369.07</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2514.81</v>
+        <v>2498.7</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>4038.64</v>
+        <v>4012.76</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>37719.11</v>
+        <v>37477.46</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1027.57</v>
+        <v>1020.99</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>6308.53</v>
+        <v>6268.11</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>4887.42</v>
+        <v>4856.11</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1739.16</v>
+        <v>1728.01</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1132.03</v>
+        <v>1124.78</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>5440.22</v>
+        <v>5405.37</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1903.5</v>
+        <v>1891.3</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>8423.5</v>
+        <v>8387.209999999999</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2237.46</v>
+        <v>2227.82</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1981.05</v>
+        <v>1972.51</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>5099.29</v>
+        <v>5077.32</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1529.79</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>7193.15</v>
+        <v>7162.16</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>23079.23</v>
+        <v>22979.8</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>1934.34</v>
+        <v>1926.01</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1294.34</v>
+        <v>1288.76</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>871.36</v>
+        <v>867.61</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>3427.34</v>
+        <v>3412.58</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>8660.92</v>
+        <v>8623.610000000001</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>5839.57</v>
+        <v>5814.41</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>8104.8</v>
+        <v>8069.88</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>1088.81</v>
+        <v>1084.12</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>46708.78</v>
+        <v>46507.56</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1760.94</v>
+        <v>1753.36</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1404.02</v>
+        <v>1397.97</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1037.12</v>
+        <v>1032.65</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>829.17</v>
+        <v>825.6</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2603.34</v>
+        <v>2565.67</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>24162.33</v>
+        <v>23812.77</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>10952.95</v>
+        <v>10794.49</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>2420.06</v>
+        <v>2385.05</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>11110.76</v>
+        <v>10950.02</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>3259.28</v>
+        <v>3212.13</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>12621.64</v>
+        <v>12439.04</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1773.39</v>
+        <v>1747.73</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>10802.54</v>
+        <v>10646.26</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>11661.41</v>
+        <v>11492.7</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>33801.39</v>
+        <v>33312.38</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>962.37</v>
+        <v>948.4400000000001</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>1490.23</v>
+        <v>1468.67</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2479.54</v>
+        <v>2443.67</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>800.53</v>
+        <v>788.95</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>5287.18</v>
+        <v>5210.69</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>20803.64</v>
+        <v>20502.67</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>5139.71</v>
+        <v>5065.35</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>5338.1</v>
+        <v>5260.88</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1825.65</v>
+        <v>1799.24</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>4995.64</v>
+        <v>4888.16</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>913.75</v>
+        <v>894.09</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>5775.71</v>
+        <v>5651.44</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1539.28</v>
+        <v>1506.16</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>4665.95</v>
+        <v>4565.56</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>3997.3</v>
+        <v>3911.3</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1168.43</v>
+        <v>1143.29</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>8698.99</v>
+        <v>8511.83</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>9900.389999999999</v>
+        <v>9687.389999999999</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>8786.629999999999</v>
+        <v>8597.59</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>929.86</v>
+        <v>909.85</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1631.9</v>
+        <v>1596.79</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2870.85</v>
+        <v>2809.09</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2411.25</v>
+        <v>2359.37</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>779.54</v>
+        <v>762.76</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>814.53</v>
+        <v>797</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>3334.97</v>
+        <v>3263.22</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1788.54</v>
+        <v>1746.92</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>30490.55</v>
+        <v>29781.06</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>16618.4</v>
+        <v>16231.71</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>1834.65</v>
+        <v>1791.96</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>801.26</v>
+        <v>782.61</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1730.9</v>
+        <v>1690.63</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>5034.25</v>
+        <v>4917.11</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>14414.6</v>
+        <v>14079.19</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>7851.71</v>
+        <v>7669.01</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1892.38</v>
+        <v>1848.34</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>10883.63</v>
+        <v>10630.38</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>2821.49</v>
+        <v>2755.84</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>3282.94</v>
+        <v>3206.55</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1674.75</v>
+        <v>1635.78</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>15636.21</v>
+        <v>15272.37</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>9187.98</v>
+        <v>8974.18</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>1490.5</v>
+        <v>1455.81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22635,7 +22635,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Feria Internacional del Aire y del Espacio</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmería</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Camino La Pólvora</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gendarmeria de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ESCUELA DE GRUMETES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA CONCON</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Vilcún</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Feria Internacional del Aire y del Espacio</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>ARCHIVO NACIONAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Cementerio General</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20993,7 +20993,7 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Administración de Fondos de Terceros</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21725,7 +21725,7 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -22325,7 +22325,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22335,7 +22335,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
@@ -623,7 +623,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1635,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1887,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1952,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2078,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2143,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2208,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2334,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2399,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2464,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2529,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2716,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3208,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3578,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3887,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4196,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4261,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4692,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5001,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5066,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5131,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5196,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5322,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5387,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5452,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5517,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5704,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6135,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6383,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6570,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6757,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6883,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6948,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7013,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7261,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7326,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7391,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7517,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7643,11 @@
           <t>77.575.038-3</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7708,11 @@
           <t>77.575.038-3</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7956,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8021,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8208,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8395,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8643,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8891,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8956,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9143,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9269,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9700,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9887,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9952,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10017,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10143,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11001,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11066,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11436,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11623,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11688,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11875,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11940,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12066,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12375,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12501,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12871,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13119,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13367,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13432,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13558,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +13871,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14241,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14306,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14371,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14436,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14501,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +14688,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +14753,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15123,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15310,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15375,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +15501,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +15688,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +15753,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +15879,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +15944,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16436,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16182,7 +16562,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16426,7 +16810,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17119,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16792,7 +17184,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17310,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +17497,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17158,7 +17562,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17280,7 +17688,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17402,7 +17814,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18001,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +18066,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17707,7 +18131,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18134,7 +18562,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +18688,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +18814,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18439,7 +18879,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +18944,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18561,7 +19009,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19074,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18805,7 +19261,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +19387,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +19574,11 @@
           <t>77.575.038-3</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +19883,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20070,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20257,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19842,7 +20322,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20387,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20452,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20025,7 +20517,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20269,7 +20765,11 @@
           <t>77.352.453-K</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +20830,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +20956,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21021,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21086,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21151,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21184,7 +21704,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21245,7 +21769,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +21834,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21611,7 +22143,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +22513,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +22578,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22404,7 +22948,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +23196,11 @@
           <t>77.103.803-4</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
@@ -4631,7 +4631,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14180,7 +14184,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14566,7 +14574,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20135,7 +20147,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21521,7 +21537,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22269,7 +22289,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22452,7 +22476,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22887,7 +22915,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2026.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -15993,7 +15993,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -19745,7 +19745,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -20310,7 +20310,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
